--- a/training_survey_templates/030_training_survey_template--training_survey_templates.xlsx
+++ b/training_survey_templates/030_training_survey_template--training_survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>training_survey_template</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>training_survey_template</t>
+          <t>What is the purpose of the training session?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>quality_rating</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>How would you rate the overall quality of the training session?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>topics_covered</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Which of the following topics were covered during the training session?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>training_hours</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>How many hours did you spend on the training session?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>form_id</t>
+          <t>On what date did the training session take place?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>start_end_time</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>What time did the training session start and end?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>facilitator_performance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>How would you rate the training facilitator's performance?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,21 +676,67 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Are there any other comments you would like to provide?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>relevance</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>How would you rate the overall relevance of the training session to your job requirements?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>effectiveness</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>How would you rate the overall effectiveness of the training session?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -707,12 +753,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -735,102 +781,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>quality_rating_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>quality_rating_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>quality_rating_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>quality_rating_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>topics_covered_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>leadership</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Leadership</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>topics_covered_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>management</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>topics_covered_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>communication</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Communication</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>topics_covered_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>time_management</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Time Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>facilitator_performance_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>excellent</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Excellent</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>facilitator_performance_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Good</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>facilitator_performance_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>facilitator_performance_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>poor</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Poor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>relevance_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>very_relevant</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Very relevant</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>relevance_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>somewhat_relevant</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Somewhat relevant</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>relevance_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>not_very_relevant</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not very relevant</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>highly_effective</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Highly effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>somewhat_effective</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Somewhat effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>effectiveness_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>not_very_effective</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Not very effective</t>
         </is>
       </c>
     </row>
